--- a/IMRADS/Map Visualizer/allocation_results.xlsx
+++ b/IMRADS/Map Visualizer/allocation_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PERSONAL\BRYAN\bulsu\Thesis 1\ShelterAlloc_Thesis\ProgramSrc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PERSONAL\BRYAN\bulsu\Thesis 1\ShelterAlloc_Thesis\IMRADS\Map Visualizer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{330254C1-CAF6-428E-8038-D3F27719E5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84074ECB-E953-4E69-9833-913E78ACD712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1425" yWindow="1185" windowWidth="21045" windowHeight="11715" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,18 +20,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
   <si>
     <t>Community</t>
   </si>
   <si>
-    <t>Allocated Population</t>
-  </si>
-  <si>
     <t>Shelter Assigned</t>
   </si>
   <si>
-    <t>Level</t>
+    <t>Doña Damiana Elem School</t>
+  </si>
+  <si>
+    <t>San Marcos Elem. Sch.</t>
+  </si>
+  <si>
+    <t>San Marcos National H.S.</t>
+  </si>
+  <si>
+    <t>NV9 Multi-Purpose</t>
+  </si>
+  <si>
+    <t>Mun. Covered Court</t>
+  </si>
+  <si>
+    <t>Balite</t>
+  </si>
+  <si>
+    <t>Balungao</t>
+  </si>
+  <si>
+    <t>Buguion</t>
+  </si>
+  <si>
+    <t>Bulusan</t>
+  </si>
+  <si>
+    <t>Calizon</t>
+  </si>
+  <si>
+    <t>Calumpang</t>
+  </si>
+  <si>
+    <t>Caniogan</t>
+  </si>
+  <si>
+    <t>Corazon</t>
+  </si>
+  <si>
+    <t>Frances</t>
+  </si>
+  <si>
+    <t>Gatbuca</t>
+  </si>
+  <si>
+    <t>Gugo</t>
+  </si>
+  <si>
+    <t>Iba Este</t>
+  </si>
+  <si>
+    <t>Iba O'Este</t>
+  </si>
+  <si>
+    <t>Longos</t>
+  </si>
+  <si>
+    <t>Meysulao</t>
+  </si>
+  <si>
+    <t>Meyto</t>
+  </si>
+  <si>
+    <t>Palimbang</t>
+  </si>
+  <si>
+    <t>Panducot</t>
+  </si>
+  <si>
+    <t>Pio Cruzcosa</t>
+  </si>
+  <si>
+    <t>Poblacion</t>
+  </si>
+  <si>
+    <t>Pungo</t>
+  </si>
+  <si>
+    <t>San Jose</t>
+  </si>
+  <si>
+    <t>San Marcos</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Santa Lucia</t>
+  </si>
+  <si>
+    <t>Santo Niño</t>
+  </si>
+  <si>
+    <t>Sapang Bayan</t>
+  </si>
+  <si>
+    <t>Sergio Bayan</t>
+  </si>
+  <si>
+    <t>Sucol</t>
   </si>
 </sst>
 </file>
@@ -433,21 +529,247 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
